--- a/data/아웃바운드_스크립트_0621.xlsx
+++ b/data/아웃바운드_스크립트_0621.xlsx
@@ -1342,7 +1342,7 @@
       <c r="C28" s="41" t="n"/>
       <c r="D28" s="13" t="inlineStr">
         <is>
-          <t>전문상담원과 직접 통화도 가능하신데요. 어떤 쪽이 편하세요?</t>
+          <t>안전한 본심사를 위해 모바일앱이나 웹에서 직접처리하시는 디지털방식과 지금 저와 대화를 이어가시는 AI상담방식중 어떤 편이 편하신가요?</t>
         </is>
       </c>
     </row>
